--- a/CBT_2022_1회/산업안전기사_2022_1회_문항등록.xlsx
+++ b/CBT_2022_1회/산업안전기사_2022_1회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="AI5" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;교육형태의 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;가정 · 학교 · 사회는 모두 「어디서」&lt;/strong&gt;를 가리키는 말이다 — &lt;strong&gt;「어떻게」를 묻는 방법과 어긋난다&lt;/strong&gt;. &lt;strong&gt;방법은 강의식 · 토의식 같은 말&lt;/strong&gt; 이라야 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가정·학교·사회는 교육장소&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;교육형태의 분류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;가정 · 학교 · 사회는 모두 「어디서」&lt;/strong&gt;를 가리키는 말이다 — &lt;strong&gt;「어떻게」를 묻는 방법과 어긋난다&lt;/strong&gt;. &lt;strong&gt;방법은 강의식 · 토의식 같은 말&lt;/strong&gt;이라야 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;가정·학교·사회는 교육장소&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
-          <t>레윈(Lewin)은 인간의 행동 특성을 「 B = f( PㆍE) 」 으로 표현 하였다. 변수 「E」가 의미하는 것으로 옳은 것은?</t>
+          <t>레윈(Lewin)은 인간의 행동 특성을 「 B = f( PㆍE) 」으로 표현 하였다. 변수 「E」가 의미하는 것으로 옳은 것은?</t>
         </is>
       </c>
       <c r="V9" s="32" t="inlineStr"/>
@@ -2221,17 +2221,17 @@
       </c>
       <c r="AG9" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;E 는 Environment&lt;/strong&gt; — &lt;strong&gt;작업환경&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;레빈의 법칙 $B = f ( P \cdot E )$&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Behavior&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;인간의 행동&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;f&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;function&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;함수&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;P&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Person&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;소질(개체) — 나이 · 성격 · 지능 · 경험 · 심신 상태&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Environment&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;환경 — 작업환경 · 인간관계 · 설비&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;E는 Environment&lt;/strong&gt; — &lt;strong&gt;작업환경&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;레빈의 법칙 $B = f ( P \cdot E )$&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;B&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Behavior&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;인간의 행동&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;f&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;function&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;함수&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;P&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Person&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;소질(개체) — 나이 · 성격 · 지능 · 경험 · 심신 상태&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Environment&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;환경 — 작업환경 · 인간관계 · 설비&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH9" s="32" t="inlineStr">
         <is>
-          <t>① 연령은 P 에 드는 것이다.&lt;br&gt;② 성격도 그렇다.&lt;br&gt;④ 지능도 그렇다.</t>
+          <t>① 연령은 P에 드는 것이다.&lt;br&gt;② 성격도 그렇다.&lt;br&gt;④ 지능도 그렇다.</t>
         </is>
       </c>
       <c r="AI9" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;레빈의 법칙&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;보기 넷 가운데 셋(연령 · 성격 · 지능)이 모두 사람의 속성&lt;/strong&gt;이라 &lt;strong&gt;하나만 남는다&lt;/strong&gt;. &lt;strong&gt;P 와 E 를 뒤바꿔 묻는 것&lt;/strong&gt;이 이 유형의 흔한 꼴이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;E 는 환경, P 는 소질&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;레빈의 법칙&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;보기 넷 가운데 셋(연령 · 성격 · 지능)이 모두 사람의 속성&lt;/strong&gt;이라 &lt;strong&gt;하나만 남는다&lt;/strong&gt;. &lt;strong&gt;P와 E를 뒤바꿔 묻는 것&lt;/strong&gt;이 이 유형의 흔한 꼴이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;E는 환경, P는 소질&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AG10" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;억측판단&lt;/strong&gt;이다. &lt;strong&gt;「괜찮겠지」하고 제멋대로 미루어 짐작&lt;/strong&gt; 한 것이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;불안전행동의 심리적 배후&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;억측판단&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;근거 없이 「괜찮겠지」하고 짐작&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;경보기가 울려도 아직 오지 않겠지&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;착오·착각&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;잘못 보거나 잘못 알았다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다른 스위치를 누른다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무의식 행동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;버릇대로 몸이 먼저 움직였다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지름길 반응&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;빨리 가려고 위험한 길로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;울타리를 넘어 질러간다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;생략행위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;귀찮아 절차를 건너뛴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;보호구를 벗고 작업&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;억측판단&lt;/strong&gt;이다. &lt;strong&gt;「괜찮겠지」하고 제멋대로 미루어 짐작&lt;/strong&gt;한 것이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;불안전행동의 심리적 배후&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;억측판단&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;근거 없이 「괜찮겠지」하고 짐작&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;경보기가 울려도 아직 오지 않겠지&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;착오·착각&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;잘못 보거나 잘못 알았다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다른 스위치를 누른다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무의식 행동&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;버릇대로 몸이 먼저 움직였다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지름길 반응&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;빨리 가려고 위험한 길로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;울타리를 넘어 질러간다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;생략행위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;귀찮아 절차를 건너뛴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;보호구를 벗고 작업&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH10" s="32" t="inlineStr">
@@ -2747,7 +2747,7 @@
       </c>
       <c r="AI13" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;산업안전보건위원회&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;명예산업안전감독관은 근로자 쪽에서 지명&lt;/strong&gt; 한다 — &lt;strong&gt;이름에 「감독관」이 들어가 사용자 쪽으로 보이기 쉬운 것&lt;/strong&gt;이 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;명예산업안전감독관은 근로자위원&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;산업안전보건위원회&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;명예산업안전감독관은 근로자 쪽에서 지명&lt;/strong&gt;한다 — &lt;strong&gt;이름에 「감독관」이 들어가 사용자 쪽으로 보이기 쉬운 것&lt;/strong&gt;이 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;명예산업안전감독관은 근로자위원&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2995,17 +2995,17 @@
       </c>
       <c r="AG15" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;외부 전문가를 강사로 부르는&lt;/strong&gt; 것은 &lt;strong&gt;Off JT&lt;/strong&gt;의 장점이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;OJT 와 Off JT&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;OJT&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off JT&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;어디서&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일하는 자리에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;따로 자리를 마련해&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직속상사가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;외부 전문가·전문 강사가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;몇 명&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;한 사람 또는 소수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여럿을 한꺼번에&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;현장 실정에 맞다 · 개별 지도 · 상호 신뢰가 두터워진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조직적·체계적 · 전문가에게 배운다 · 여러 매체&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;외부 전문가를 강사로 부르는&lt;/strong&gt; 것은 &lt;strong&gt;Off JT&lt;/strong&gt;의 장점이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;OJT와 Off JT&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;OJT&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off JT&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;어디서&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일하는 자리에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;따로 자리를 마련해&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직속상사가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;외부 전문가·전문 강사가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;몇 명&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;한 사람 또는 소수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여럿을 한꺼번에&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;현장 실정에 맞다 · 개별 지도 · 상호 신뢰가 두터워진다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조직적·체계적 · 전문가에게 배운다 · 여러 매체&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH15" s="32" t="inlineStr">
         <is>
-          <t>① 상호 신뢰와 이해도가 높아지는 것은 OJT 의 특징이다.&lt;br&gt;② 개개인에 맞춘 지도훈련이 가능한 것도 그렇다.&lt;br&gt;③ 사업장 실정에 맞는 실제적 훈련이 가능한 것도 그렇다.</t>
+          <t>① 상호 신뢰와 이해도가 높아지는 것은 OJT의 특징이다.&lt;br&gt;② 개개인에 맞춘 지도훈련이 가능한 것도 그렇다.&lt;br&gt;③ 사업장 실정에 맞는 실제적 훈련이 가능한 것도 그렇다.</t>
         </is>
       </c>
       <c r="AI15" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;OJT 와 Off JT&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「외부」 · 「전문가」 · 「다수」 · 「체계적」&lt;/strong&gt;이라는 낱말이 나오면 Off JT 다 — &lt;strong&gt;OJT 는 「우리 현장, 우리 상사, 나 한 사람」&lt;/strong&gt;이 전부다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;외부 전문가 초빙은 Off JT&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;OJT와 Off JT&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「외부」 · 「전문가」 · 「다수」 · 「체계적」&lt;/strong&gt;이라는 낱말이 나오면 Off JT다 — &lt;strong&gt;OJT는 「우리 현장, 우리 상사, 나 한 사람」&lt;/strong&gt;이 전부다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;외부 전문가 초빙은 Off JT&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AG18" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;연삭기&lt;/strong&gt; 자체는 안전인증 대상이 아니다. &lt;strong&gt;연삭기 덮개가 자율안전확인 대상 방호장치&lt;/strong&gt; 일 뿐이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전인증 대상 기계·기구 및 설비&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;프레스 · 전단기 및 절곡기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;크레인 · 리프트 · 곤돌라 · 고소작업대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;압력용기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;롤러기 · 사출성형기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기계톱(이동식)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연삭기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전인증 대상이 아니다&lt;/u&gt; — 덮개가 자율안전확인 대상 방호장치&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;연삭기&lt;/strong&gt; 자체는 안전인증 대상이 아니다. &lt;strong&gt;연삭기 덮개가 자율안전확인 대상 방호장치&lt;/strong&gt;일 뿐이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전인증 대상 기계·기구 및 설비&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;프레스 · 전단기 및 절곡기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;크레인 · 리프트 · 곤돌라 · 고소작업대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;압력용기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;롤러기 · 사출성형기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기계톱(이동식)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연삭기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전인증 대상이 아니다&lt;/u&gt; — 덮개가 자율안전확인 대상 방호장치&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH18" s="32" t="inlineStr">
@@ -3769,17 +3769,17 @@
       </c>
       <c r="AG21" s="32" t="inlineStr">
         <is>
-          <t>전체는 330건이므로 $\dfrac{29}{330} \times 100 \fallingdotseq 8.8$ [%] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;하인리히의 1 : 29 : 300&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;건수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비율&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;중상 또는 사망&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.3%&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;경상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;29&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;8.8%&lt;/u&gt; — 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무상해사고(아차사고)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;90.9%&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;합계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;330&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100%&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>전체는 330건이므로 $\dfrac{29}{330} \times 100 \fallingdotseq 8.8$ [%]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;하인리히의 1 : 29 : 300&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;건수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;비율&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;중상 또는 사망&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.3%&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;경상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;29&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;8.8%&lt;/u&gt; — 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무상해사고(아차사고)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;300&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;90.9%&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;합계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;330&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;100%&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH21" s="32" t="inlineStr">
         <is>
-          <t>② 9.8% 는 계산과 맞지 않는다.&lt;br&gt;③ 10.8% 도 그렇다.&lt;br&gt;④ 11.8% 도 그렇다.</t>
+          <t>② 9.8%는 계산과 맞지 않는다.&lt;br&gt;③ 10.8% 도 그렇다.&lt;br&gt;④ 11.8% 도 그렇다.</t>
         </is>
       </c>
       <c r="AI21" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;하인리히의 재해구성비율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;분모가 330 이라는 것&lt;/strong&gt;만 놓치지 않으면 된다 — &lt;strong&gt;29 를 300 으로 나누면 9.7% 가 나와 ②로 끌린다&lt;/strong&gt;. &lt;strong&gt;버드의 1 : 10 : 30 : 600&lt;/strong&gt;도 짝으로 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;29 ÷ 330 = 8.8%&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;하인리히의 재해구성비율&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;분모가 330이라는 것&lt;/strong&gt;만 놓치지 않으면 된다 — &lt;strong&gt;29를 300으로 나누면 9.7%가 나와 ②로 끌린다&lt;/strong&gt;. &lt;strong&gt;버드의 1 : 10 : 30 : 600&lt;/strong&gt;도 짝으로 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;29 ÷ 330 = 8.8%&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4031,17 +4031,17 @@
       </c>
       <c r="AG23" s="32" t="inlineStr">
         <is>
-          <t>A 는 AND 이므로 $0.015 \times 0.02 = 0.0003$ 이다. T 는 OR 이므로 $1 - ( 1 - 0.0003 ) ( 1 - 0.05 ) \fallingdotseq 0.0503$ 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;게이트별 확률 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;게이트&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AND&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$P = P_{1} \times P_{2} \times \cdots$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모두 일어나야 하므로 곱한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;OR&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$P = 1 - ( 1 - P_{1} ) ( 1 - P_{2} ) \cdots$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하나라도 일어나면 되므로 여사상을 곱해 뺀다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;A(AND)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.015 × 0.02 = 0.0003&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T(OR)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 − 0.9997 × 0.95 = 0.0503&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>A는 AND이므로 $0.015 \times 0.02 = 0.0003$이다. T는 OR이므로 $1 - ( 1 - 0.0003 ) ( 1 - 0.05 ) \fallingdotseq 0.0503$이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;게이트별 확률 계산&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;게이트&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AND&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$P = P_{1} \times P_{2} \times \cdots$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모두 일어나야 하므로 곱한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;OR&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$P = 1 - ( 1 - P_{1} ) ( 1 - P_{2} ) \cdots$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하나라도 일어나면 되므로 여사상을 곱해 뺀다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;A(AND)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.015 × 0.02 = 0.0003&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;T(OR)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1 − 0.9997 × 0.95 = 0.0503&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH23" s="32" t="inlineStr">
         <is>
-          <t>① 0.0002 는 계산과 맞지 않는다.&lt;br&gt;② 0.0283 도 그렇다.&lt;br&gt;④ 0.950 은 3번 사상이 일어나지 않을 확률이다.</t>
+          <t>① 0.0002는 계산과 맞지 않는다.&lt;br&gt;② 0.0283 도 그렇다.&lt;br&gt;④ 0.950은 3번 사상이 일어나지 않을 확률이다.</t>
         </is>
       </c>
       <c r="AI23" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FT 의 확률 계산&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;OR 은 확률이 작을 때 「그냥 더한 값」과 거의 같다&lt;/strong&gt; — &lt;strong&gt;0.0003 + 0.05 = 0.0503&lt;/strong&gt;. &lt;strong&gt;AND 에서 나온 0.0003 이 워낙 작아 결과를 거의 바꾸지 못한다&lt;/strong&gt;는 점도 눈여겨볼 만하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;AND 는 곱하고 OR 은 여사상으로&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FT의 확률 계산&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;OR은 확률이 작을 때 「그냥 더한 값」과 거의 같다&lt;/strong&gt; — &lt;strong&gt;0.0003 + 0.05 = 0.0503&lt;/strong&gt;. &lt;strong&gt;AND에서 나온 0.0003이 워낙 작아 결과를 거의 바꾸지 못한다&lt;/strong&gt;는 점도 눈여겨볼 만하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;AND는 곱하고 OR은 여사상으로&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4160,7 +4160,7 @@
       </c>
       <c r="AG24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정상사상(Top event)을 정의&lt;/strong&gt; 하는 것이 먼저다. &lt;strong&gt;무엇을 막을지 정해야 나무를 그릴 수&lt;/strong&gt; 있다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA 의 절차&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;차례&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정상사상(Top event)을 정의한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;구체적이고 명확하게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시스템을 이해하고 자료를 모은다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FT 도를 작성한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;논리게이트로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;컷셋을 구한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;미니멀 컷셋을 구한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;불 대수로 간소화&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적·정량적으로 평가하고 대책을 세운다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;정상사상(Top event)을 정의&lt;/strong&gt;하는 것이 먼저다. &lt;strong&gt;무엇을 막을지 정해야 나무를 그릴 수&lt;/strong&gt; 있다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FTA의 절차&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;차례&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정상사상(Top event)을 정의한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;구체적이고 명확하게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시스템을 이해하고 자료를 모은다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FT 도를 작성한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;논리게이트로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;컷셋을 구한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;미니멀 컷셋을 구한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;불 대수로 간소화&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적·정량적으로 평가하고 대책을 세운다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH24" s="32" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AI24" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 의 절차&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;FTA 는 「결과에서 원인으로 거슬러 올라가는」 연역적 기법&lt;/strong&gt;이다 — &lt;strong&gt;출발점인 결과(정상사상)를 정하지 않고는 아무것도 시작할 수&lt;/strong&gt; 없다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;정상사상 정의가 첫걸음&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA의 절차&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;FTA는 「결과에서 원인으로 거슬러 올라가는」 연역적 기법&lt;/strong&gt;이다 — &lt;strong&gt;출발점인 결과(정상사상)를 정하지 않고는 아무것도 시작할 수&lt;/strong&gt; 없다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;정상사상 정의가 첫걸음&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="AH29" s="32" t="inlineStr">
         <is>
-          <t>① 가속도가 운동 변화율인 것은 맞다.&lt;br&gt;② 1 G 가 9.8 [m/s²] 인 것도 맞다.&lt;br&gt;④ 전후방 선형가속의 영향이 수직방향보다 덜한 것도 맞다.</t>
+          <t>① 가속도가 운동 변화율인 것은 맞다.&lt;br&gt;② 1 G가 9.8 [m/s²] 인 것도 맞다.&lt;br&gt;④ 전후방 선형가속의 영향이 수직방향보다 덜한 것도 맞다.</t>
         </is>
       </c>
       <c r="AI29" s="32" t="inlineStr">
@@ -4910,17 +4910,17 @@
       </c>
       <c r="AG30" s="32" t="inlineStr">
         <is>
-          <t>정상사상의 확률은 $0.05 \times 0.08 = 0.004$ 이므로 신뢰도는 $1 - 0.004 = 0.996$ 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;고장확률과 신뢰도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AND 조합&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$P_{T} = 0.05 \times 0.08 = 0.004$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;두 사상이 함께 일어나야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;신뢰도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R = 1 - P_{T} = 0.996$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고장나지 않을 확률&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;OR 이었다면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$P_{T} = 1 - 0.95 \times 0.92 = 0.126$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②가 그 값&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>정상사상의 확률은 $0.05 \times 0.08 = 0.004$이므로 신뢰도는 $1 - 0.004 = 0.996$이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;고장확률과 신뢰도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;AND 조합&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$P_{T} = 0.05 \times 0.08 = 0.004$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;두 사상이 함께 일어나야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;신뢰도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R = 1 - P_{T} = 0.996$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;고장나지 않을 확률&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;OR 이었다면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$P_{T} = 1 - 0.95 \times 0.92 = 0.126$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②가 그 값&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH30" s="32" t="inlineStr">
         <is>
-          <t>① 0.004 는 정상사상의 확률이지 신뢰도가 아니다.&lt;br&gt;② 0.126 은 OR 조합일 때의 고장확률이다.&lt;br&gt;③ 0.874 는 OR 조합일 때의 신뢰도다.</t>
+          <t>① 0.004는 정상사상의 확률이지 신뢰도가 아니다.&lt;br&gt;② 0.126은 OR 조합일 때의 고장확률이다.&lt;br&gt;③ 0.874는 OR 조합일 때의 신뢰도다.</t>
         </is>
       </c>
       <c r="AI30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FTA 와 신뢰도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;보기 넷이 「AND 고장 · OR 고장 · OR 신뢰도 · AND 신뢰도」&lt;/strong&gt; 네 값으로 짜여 있다 — &lt;strong&gt;AND 인지 OR 인지, 고장인지 신뢰도인지 두 갈래를 모두 맞춰야&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;신뢰도 = 1 − 고장확률&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FTA와 신뢰도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;보기 넷이 「AND 고장 · OR 고장 · OR 신뢰도 · AND 신뢰도」&lt;/strong&gt; 네 값으로 짜여 있다 — &lt;strong&gt;AND 인지 OR 인지, 고장인지 신뢰도인지 두 갈래를 모두 맞춰야&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;신뢰도 = 1 − 고장확률&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5039,7 @@
       </c>
       <c r="AG31" s="32" t="inlineStr">
         <is>
-          <t>다섯째는 &lt;strong&gt;신규설계의 정도&lt;/strong&gt;이지 &lt;strong&gt;「가능성」이 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FMEA 고장평점법의 다섯 평가요소&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;평가요소&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기능적 고장 영향의 중요도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;영향을 미치는 시스템의 범위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고장발생의 빈도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고장방지의 가능성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;신규설계의 정도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「신규설계의 가능성」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;평점&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$C = ( C_{1} C_{2} C_{3} C_{4} C_{5} )^{1 / 5}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다섯 값의 기하평균&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>다섯째는 &lt;strong&gt;신규설계의 정도&lt;/strong&gt;이지 &lt;strong&gt;「가능성」이 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FMEA 고장평점법의 다섯 평가요소&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;평가요소&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기능적 고장 영향의 중요도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;영향을 미치는 시스템의 범위&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고장발생의 빈도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고장방지의 가능성&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;신규설계의 정도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「신규설계의 가능성」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;평점&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$C = ( C_{1} C_{2} C_{3} C_{4} C_{5} )^{1 / 5}$ — 다섯 값의 기하평균&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH31" s="32" t="inlineStr">
@@ -5049,7 +5049,7 @@
       </c>
       <c r="AI31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FMEA 의 고장평점법&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「가능성」이 붙는 요소는 「고장방지의 가능성」 하나뿐&lt;/strong&gt;이다 — &lt;strong&gt;신규설계는 「얼마나 새로운 설계인가」를 재는 것이라 「정도」&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;신규설계는 「정도」&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FMEA의 고장평점법&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「가능성」이 붙는 요소는 「고장방지의 가능성」 하나뿐&lt;/strong&gt;이다 — &lt;strong&gt;신규설계는 「얼마나 새로운 설계인가」를 재는 것이라 「정도」&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;신규설계는 「정도」&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="AG32" s="32" t="inlineStr">
         <is>
-          <t>정미가동률은 $\dfrac{\text{생산량} \times \text{실제 주기시간}}{\text{가동시간}}$ 이다. &lt;strong&gt;「기준 주기시간」이 아니라 「실제 주기시간」&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;설비종합효율&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;시간가동률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{부하시간} - \text{정지시간}}{\text{부하시간}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;속도가동률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{기준 주기시간}}{\text{실제 주기시간}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정미가동률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{생산량} \times \text{실제 주기시간}}{\text{가동시간}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「기준」이 아니라 「실제」&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;성능가동률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;속도가동률 × 정미가동률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설비종합효율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시간가동률 × 성능가동률 × 양품률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>정미가동률은 $\dfrac{\text{생산량} \times \text{실제 주기시간}}{\text{가동시간}}$이다. &lt;strong&gt;「기준 주기시간」이 아니라 「실제 주기시간」&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;설비종합효율&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;시간가동률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{부하시간} - \text{정지시간}}{\text{부하시간}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;속도가동률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{기준 주기시간}}{\text{실제 주기시간}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정미가동률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{생산량} \times \text{실제 주기시간}}{\text{가동시간}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「기준」이 아니라 「실제」&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;성능가동률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;속도가동률 × 정미가동률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설비종합효율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시간가동률 × 성능가동률 × 양품률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH32" s="32" t="inlineStr">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="AG33" s="32" t="inlineStr">
         <is>
-          <t>총 가동시간은 $24 \times 4 {,} 000 = 96 {,} 000$ 시간이다. $\mathrm{MTTF} = \dfrac{96 {,} 000}{14} \fallingdotseq 6 {,} 857$ 시간이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;MTTF 의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;총 가동시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;24 × 4,000 = 96,000 시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;회로 수를 곱해야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;MTTF&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;96,000 ÷ 14 = 6,857 시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고장률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\lambda = \dfrac{14}{96 {,} 000} = 1.46 \times 10^{-4}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;/시간&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>총 가동시간은 $24 \times 4 {,} 000 = 96 {,} 000$ 시간이다. $\mathrm{MTTF} = \dfrac{96 {,} 000}{14} \fallingdotseq 6 {,} 857$ 시간이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;MTTF의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;총 가동시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;24 × 4,000 = 96,000 시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;회로 수를 곱해야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;MTTF&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;96,000 ÷ 14 = 6,857 시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고장률&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\lambda = \dfrac{14}{96 {,} 000} = 1.46 \times 10^{-4}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;/시간&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH33" s="32" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="AI33" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;평균 고장시간(MTTF)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「24개」라는 수를 곱하지 않고 4,000 ÷ 14 로 가면 286 이 나와 보기에 없다&lt;/strong&gt; — &lt;strong&gt;여러 개를 동시에 돌렸으면 총 가동시간은 개수 × 시간&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;총 가동시간 = 개수 × 시간&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;평균 고장시간(MTTF)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「24개」라는 수를 곱하지 않고 4,000 ÷ 14로 가면 286이 나와 보기에 없다&lt;/strong&gt; — &lt;strong&gt;여러 개를 동시에 돌렸으면 총 가동시간은 개수 × 시간&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;총 가동시간 = 개수 × 시간&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5431,7 @@
       </c>
       <c r="AH34" s="32" t="inlineStr">
         <is>
-          <t>② 20 ~ 80 %tile 은 너무 좁아 쓰는 사람의 60%만 아우른다.&lt;br&gt;③ 30 ~ 70 %tile 은 더 좁다.&lt;br&gt;④ 40 ~ 60 %tile 은 거의 평균치에 가깝다.</t>
+          <t>② 20 ~ 80 %tile은 너무 좁아 쓰는 사람의 60%만 아우른다.&lt;br&gt;③ 30 ~ 70 %tile은 더 좁다.&lt;br&gt;④ 40 ~ 60 %tile은 거의 평균치에 가깝다.</t>
         </is>
       </c>
       <c r="AI34" s="32" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="AH35" s="32" t="inlineStr">
         <is>
-          <t>① 수평거리는 RWL 의 계수다.&lt;br&gt;② 수직거리도 그렇다.&lt;br&gt;④ 비대칭각도도 그렇다.</t>
+          <t>① 수평거리는 RWL의 계수다.&lt;br&gt;② 수직거리도 그렇다.&lt;br&gt;④ 비대칭각도도 그렇다.</t>
         </is>
       </c>
       <c r="AI35" s="32" t="inlineStr">
@@ -5684,17 +5684,17 @@
       </c>
       <c r="AG36" s="32" t="inlineStr">
         <is>
-          <t>$WD = 0.85 W + 0.15 D = 0.85 \times 20 + 0.15 \times 24 = 20.6$ [℃] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;열환경 지수&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;옥스퍼드 지수(WD)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$WD = 0.85 W + 0.15 D$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;W 는 습구, D 는 건구&lt;/u&gt; · 습구에 크게 기운다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;습구흑구온도지수(WBGT)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;옥외(햇빛 있음): 0.7 자연습구 + 0.2 흑구 + 0.1 건구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;옥내: 0.7 자연습구 + 0.3 흑구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;불쾌지수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.72(건구 + 습구) + 40.6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$WD = 0.85 W + 0.15 D = 0.85 \times 20 + 0.15 \times 24 = 20.6$ [℃]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;열환경 지수&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;지수&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;옥스퍼드 지수(WD)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$WD = 0.85 W + 0.15 D$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;W는 습구, D는 건구&lt;/u&gt; · 습구에 크게 기운다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;습구흑구온도지수(WBGT)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;옥외(햇빛 있음): 0.7 자연습구 + 0.2 흑구 + 0.1 건구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;옥내: 0.7 자연습구 + 0.3 흑구&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;불쾌지수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.72(건구 + 습구) + 40.6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH36" s="32" t="inlineStr">
         <is>
-          <t>② 21.0 [℃] 는 계산과 맞지 않는다.&lt;br&gt;③ 23.0 [℃] 도 그렇다.&lt;br&gt;④ 23.4 [℃] 는 계수를 뒤바꾼 값이다.</t>
+          <t>② 21.0 [℃]는 계산과 맞지 않는다.&lt;br&gt;③ 23.0 [℃] 도 그렇다.&lt;br&gt;④ 23.4 [℃]는 계수를 뒤바꾼 값이다.</t>
         </is>
       </c>
       <c r="AI36" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;옥스퍼드 지수(WD)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;계수 0.85 가 습구에 붙는다&lt;/strong&gt; — &lt;strong&gt;더울 때 사람을 괴롭히는 것은 온도보다 습도&lt;/strong&gt; 이기 때문이다. &lt;strong&gt;0.15 를 건구에 붙이면 23.4 가 나와 ④로 끌린다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;습구 0.85, 건구 0.15&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;옥스퍼드 지수(WD)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;계수 0.85가 습구에 붙는다&lt;/strong&gt; — &lt;strong&gt;더울 때 사람을 괴롭히는 것은 온도보다 습도&lt;/strong&gt; 이기 때문이다. &lt;strong&gt;0.15를 건구에 붙이면 23.4가 나와 ④로 끌린다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;습구 0.85, 건구 0.15&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="AG38" s="32" t="inlineStr">
         <is>
-          <t>차례대로 놓으면 &lt;strong&gt;관계 자료의 작성준비 → 정성적 평가 → 정량적 평가 → 안전대책 → 재평가&lt;/strong&gt;이므로 4단계는 &lt;strong&gt;안전대책&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전성 평가의 6단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관계 자료의 작성준비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;도면 · 목록 · 물성 자료&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입지조건 · 공장 내 배치 · 건조물 · 소방설비 · 원재료 · 공정&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정량적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;물질 · 용량 · 온도 · 압력 · 조작&lt;/u&gt; 다섯을 점수로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설비대책 · 관리적 대책&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;재해정보에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FTA 에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>차례대로 놓으면 &lt;strong&gt;관계 자료의 작성준비 → 정성적 평가 → 정량적 평가 → 안전대책 → 재평가&lt;/strong&gt;이므로 4단계는 &lt;strong&gt;안전대책&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전성 평가의 6단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관계 자료의 작성준비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;도면 · 목록 · 물성 자료&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입지조건 · 공장 내 배치 · 건조물 · 소방설비 · 원재료 · 공정&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정량적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;물질 · 용량 · 온도 · 압력 · 조작&lt;/u&gt; 다섯을 점수로&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;설비대책 · 관리적 대책&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;재해정보에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FTA에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH38" s="32" t="inlineStr">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="U39" s="32" t="inlineStr">
         <is>
-          <t>인간의 반응시간을 조사하는 실험에서 0.1, 0.2, 0.3, 0.4 의 점등확률을 갖는 4개의 전등이 있다. 이 자극 전등이 전달하는 정보량은 약 얼마인가?</t>
+          <t>인간의 반응시간을 조사하는 실험에서 0.1, 0.2, 0.3, 0.4의 점등확률을 갖는 4개의 전등이 있다. 이 자극 전등이 전달하는 정보량은 약 얼마인가?</t>
         </is>
       </c>
       <c r="V39" s="32" t="inlineStr"/>
@@ -6075,17 +6075,17 @@
       </c>
       <c r="AG39" s="32" t="inlineStr">
         <is>
-          <t>$H = \sum p_{i} \log_{2} \dfrac{1}{p_{i}}$ 이다. $0.1 \times 3.32 + 0.2 \times 2.32 + 0.3 \times 1.74 + 0.4 \times 1.32 \fallingdotseq 1.85$ [bit] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정보량의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;확률&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;$\log_{2} ( 1 / p )$&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;곱&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0.1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3.32&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.332&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0.2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.32&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.464&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0.3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.74&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.522&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.32&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.528&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;합&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.85 [bit]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$H = \sum p_{i} \log_{2} \dfrac{1}{p_{i}}$이다. $0.1 \times 3.32 + 0.2 \times 2.32 + 0.3 \times 1.74 + 0.4 \times 1.32 \fallingdotseq 1.85$ [bit]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정보량의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;확률&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;$\log_{2} ( 1 / p )$&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;곱&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0.1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;3.32&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.332&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0.2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.32&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.464&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0.3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.74&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.522&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;0.4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.32&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;0.528&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;합&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.85 [bit]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH39" s="32" t="inlineStr">
         <is>
-          <t>① 2.42 [bit] 는 계산과 맞지 않는다.&lt;br&gt;② 2.16 [bit] 도 그렇다.&lt;br&gt;④ 1.53 [bit] 도 그렇다.</t>
+          <t>① 2.42 [bit]는 계산과 맞지 않는다.&lt;br&gt;② 2.16 [bit] 도 그렇다.&lt;br&gt;④ 1.53 [bit] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI39" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정보량(information)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;확률이 모두 같으면 &lt;/strong&gt;$H = \log_{2} 4 = 2$&lt;strong&gt; [bit] 가 최대&lt;/strong&gt;다 — &lt;strong&gt;치우쳐 있으면 그보다 작아지므로 답은 2 보다 작아야&lt;/strong&gt; 한다. &lt;strong&gt;①②가 그것만으로 걸러진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $H = \sum p_{i} \log_{2} ( 1 / p_{i} )$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정보량(information)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;확률이 모두 같으면 &lt;/strong&gt;$H = \log_{2} 4 = 2$&lt;strong&gt; [bit]가 최대&lt;/strong&gt;다 — &lt;strong&gt;치우쳐 있으면 그보다 작아지므로 답은 2보다 작아야&lt;/strong&gt; 한다. &lt;strong&gt;①②가 그것만으로 걸러진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $H = \sum p_{i} \log_{2} ( 1 / p_{i} )$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="AG40" s="32" t="inlineStr">
         <is>
-          <t>FMEA 는 &lt;strong&gt;한 번에 부품 하나의 고장&lt;/strong&gt;만 본다. &lt;strong&gt;둘 이상이 동시에 고장 나는 경우에는 맞지 않는다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FMEA 의 특징&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무엇&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;부품의 고장 형태와 그것이 시스템에 미치는 영향을 표로 정리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적 · 귀납적&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;장점&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;양식이 간단하고 특별한 훈련 없이 쓸 수 있다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단점&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;두 가지 이상이 동시에 고장 나는 경우에는 맞지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;해석 영역이 물체에 한정되어 인적 원인 해석이 어렵다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;FTA 와 다른 점&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FMEA 는 원인에서 결과로(귀납), FTA 는 결과에서 원인으로(연역)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>FMEA는 &lt;strong&gt;한 번에 부품 하나의 고장&lt;/strong&gt;만 본다. &lt;strong&gt;둘 이상이 동시에 고장 나는 경우에는 맞지 않는다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;FMEA의 특징&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무엇&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;부품의 고장 형태와 그것이 시스템에 미치는 영향을 표로 정리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적 · 귀납적&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;장점&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;양식이 간단하고 특별한 훈련 없이 쓸 수 있다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;단점&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;두 가지 이상이 동시에 고장 나는 경우에는 맞지 않는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;해석 영역이 물체에 한정되어 인적 원인 해석이 어렵다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;FTA와 다른 점&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FMEA는 원인에서 결과로(귀납), FTA는 결과에서 원인으로(연역)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH40" s="32" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="AI40" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;FMEA(고장형태와 영향분석)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;FMEA 는 부품 목록을 한 줄씩 짚어 「이것이 고장 나면?」&lt;/strong&gt;을 묻는다 — &lt;strong&gt;표의 한 줄이 부품 하나이므로 동시 고장은 담기지 않는다&lt;/strong&gt;. &lt;strong&gt;그것을 다루려면 FTA&lt;/strong&gt;로 간다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FMEA 는 동시 고장에 약하다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;FMEA(고장형태와 영향분석)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;FMEA는 부품 목록을 한 줄씩 짚어 「이것이 고장 나면?」&lt;/strong&gt;을 묻는다 — &lt;strong&gt;표의 한 줄이 부품 하나이므로 동시 고장은 담기지 않는다&lt;/strong&gt;. &lt;strong&gt;그것을 다루려면 FTA&lt;/strong&gt;로 간다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;FMEA는 동시 고장에 약하다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="AI42" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;작업면의 조도기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「750 · 300 · 150 · 75」&lt;/strong&gt; 네 숫자다 — &lt;strong&gt;아래에서부터 75 를 두 배씩 올린 값(75 → 150 → 300)에 750 만 따로&lt;/strong&gt; 붙는다고 새기면 외우기 쉽다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;초정밀 750, 정밀 300, 보통 150, 그 밖 75&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;작업면의 조도기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「750 · 300 · 150 · 75」&lt;/strong&gt; 네 숫자다 — &lt;strong&gt;아래에서부터 75를 두 배씩 올린 값(75 → 150 → 300)에 750 만 따로&lt;/strong&gt; 붙는다고 새기면 외우기 쉽다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;초정밀 750, 정밀 300, 보통 150, 그 밖 75&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="AI43" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;목재가공용 둥근톱의 분할날&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;분할날은 켠 자리가 다시 오므라들어 톱을 물지 않게 벌려 주는&lt;/strong&gt; 쇳조각이다 — &lt;strong&gt;톱날 뒤쪽에 붙는다&lt;/strong&gt;. &lt;strong&gt;덮개는 톱날 위를 덮는 것&lt;/strong&gt;이라 「가공재 윗면과의 간격」을 말한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;덮개 하단 8 [mm] 는 덮개 조건&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;목재가공용 둥근톱의 분할날&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;분할날은 켠 자리가 다시 오므라들어 톱을 물지 않게 벌려 주는&lt;/strong&gt; 쇳조각이다 — &lt;strong&gt;톱날 뒤쪽에 붙는다&lt;/strong&gt;. &lt;strong&gt;덮개는 톱날 위를 덮는 것&lt;/strong&gt;이라 「가공재 윗면과의 간격」을 말한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;덮개 하단 8 [mm]는 덮개 조건&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6849,17 +6849,17 @@
       </c>
       <c r="AG45" s="32" t="inlineStr">
         <is>
-          <t>$V = \dfrac{\pi D N}{1 {,} 000 \times 60} = \dfrac{\pi \times 30 \times 500}{60 {,} 000} \fallingdotseq 0.785$ [m/s] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;원주속도의 단위&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구할 단위&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;[m/min]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V = \dfrac{\pi D N}{1 {,} 000}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항이면 47.12&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;[m/s]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V = \dfrac{\pi D N}{1 {,} 000 \times 60}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항이면 0.785&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주의&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;D 는 [mm], N 은 [rpm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$V = \dfrac{\pi D N}{1 {,} 000 \times 60} = \dfrac{\pi \times 30 \times 500}{60 {,} 000} \fallingdotseq 0.785$ [m/s]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;원주속도의 단위&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구할 단위&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;[m/min]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V = \dfrac{\pi D N}{1 {,} 000}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항이면 47.12&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;[m/s]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$V = \dfrac{\pi D N}{1 {,} 000 \times 60}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항이면 0.785&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주의&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;D는 [mm], N은 [rpm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH45" s="32" t="inlineStr">
         <is>
-          <t>① 0.628 [m/s] 는 계산과 맞지 않는다.&lt;br&gt;③ 23.56 [m/s] 는 자릿수가 어긋난다.&lt;br&gt;④ 47.12 는 [m/min] 값이다.</t>
+          <t>① 0.628 [m/s]는 계산과 맞지 않는다.&lt;br&gt;③ 23.56 [m/s]는 자릿수가 어긋난다.&lt;br&gt;④ 47.12는 [m/min] 값이다.</t>
         </is>
       </c>
       <c r="AI45" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;선반의 원주속도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;[m/s] 를 물었는데 [m/min] 값이 보기에 함께 놓여&lt;/strong&gt; 있다 — &lt;strong&gt;60 으로 나누는 것을 잊으면 ④로 끌린다&lt;/strong&gt;. &lt;strong&gt;단위를 먼저 확인하는 것&lt;/strong&gt;이 이 유형의 요령이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;[m/s] 는 60 으로 더 나눈다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;선반의 원주속도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;[m/s]를 물었는데 [m/min] 값이 보기에 함께 놓여&lt;/strong&gt; 있다 — &lt;strong&gt;60으로 나누는 것을 잊으면 ④로 끌린다&lt;/strong&gt;. &lt;strong&gt;단위를 먼저 확인하는 것&lt;/strong&gt;이 이 유형의 요령이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;[m/s]는 60으로 더 나눈다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="AG46" s="32" t="inlineStr">
         <is>
-          <t>수인끈은 &lt;strong&gt;지름 4 [mm] 이상&lt;/strong&gt; 이라야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;프레스 방호장치의 성능기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;양수조작식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;누름버튼 사이의 안쪽 거리 300 [mm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1행정 1정지기구를 갖춘 프레스에 쓴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수인식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수인끈은 합성섬유로 지름 4 [mm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「2 [mm]」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;분당 행정수 120 이하, 행정길이 50 [mm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;손쳐내기식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;분당 행정수 120 이하, 행정길이 40 [mm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>수인끈은 &lt;strong&gt;지름 4 [mm] 이상&lt;/strong&gt;이라야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;프레스 방호장치의 성능기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;장치&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;양수조작식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;누름버튼 사이의 안쪽 거리 300 [mm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1행정 1정지기구를 갖춘 프레스에 쓴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수인식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;수인끈은 합성섬유로 지름 4 [mm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「2 [mm]」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;분당 행정수 120 이하, 행정길이 50 [mm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;손쳐내기식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;분당 행정수 120 이하, 행정길이 40 [mm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH46" s="32" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="AH48" s="32" t="inlineStr">
         <is>
-          <t>① 1.5 [m] 는 사람이 지나기에 낮다.&lt;br&gt;③ 2.5 [m] 는 기준보다 높다.&lt;br&gt;④ 3.0 [m] 도 그렇다.</t>
+          <t>① 1.5 [m]는 사람이 지나기에 낮다.&lt;br&gt;③ 2.5 [m]는 기준보다 높다.&lt;br&gt;④ 3.0 [m] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI48" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;옥내통로의 설치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;2 [m] 는 사람이 서서 다닐 수 있는 높이&lt;/strong&gt;다 — &lt;strong&gt;파이프나 덕트가 그 아래로 지나면 머리를 부딪친다&lt;/strong&gt;. &lt;strong&gt;조명 75 [lux] 와 짝으로&lt;/strong&gt; 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;옥내통로는 높이 2 [m] 이내에 장애물 금지&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;옥내통로의 설치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;2 [m]는 사람이 서서 다닐 수 있는 높이&lt;/strong&gt;다 — &lt;strong&gt;파이프나 덕트가 그 아래로 지나면 머리를 부딪친다&lt;/strong&gt;. &lt;strong&gt;조명 75 [lux]와 짝으로&lt;/strong&gt; 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;옥내통로는 높이 2 [m] 이내에 장애물 금지&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7365,12 +7365,12 @@
       </c>
       <c r="AG49" s="32" t="inlineStr">
         <is>
-          <t>$Y = 6 + 0.15 X$ 이므로 $15 = 6 + 0.15 X$, $X = 60$ [mm] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가드의 개구부 간격&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험점이 전동체가 아닐 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 6 + 0.15 X$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;X &amp;lt; 160 [mm]&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 30$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$X \ge 160$ [mm]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험점이 전동체일 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 6 + 0.1 X$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$X &amp;lt; 760$ [mm]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;X 는 가드와 위험점 사이의 거리, Y 는 개구부 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$Y = 6 + 0.15 X$이므로 $15 = 6 + 0.15 X$, $X = 60$ [mm]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;가드의 개구부 간격&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험점이 전동체가 아닐 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 6 + 0.15 X$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;X &amp;lt; 160 [mm]&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 30$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$X \ge 160$ [mm]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험점이 전동체일 때&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$Y = 6 + 0.1 X$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$X &amp;lt; 760$ [mm]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;기호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;X는 가드와 위험점 사이의 거리, Y는 개구부 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH49" s="32" t="inlineStr">
         <is>
-          <t>① 15 [mm] 는 개구부 간격 자체다.&lt;br&gt;② 30 [mm] 는 계산과 맞지 않는다.&lt;br&gt;④ 90 [mm] 도 그렇다.</t>
+          <t>① 15 [mm]는 개구부 간격 자체다.&lt;br&gt;② 30 [mm]는 계산과 맞지 않는다.&lt;br&gt;④ 90 [mm] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI49" s="32" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="AI50" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;공기스프링&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;공기는 위아래로 눌리는 데는 잘 버티지만 옆으로 밀리면 주머니가 그대로 기운다&lt;/strong&gt; — &lt;strong&gt;그래서 옆방향을 잡아 줄 다른 장치가 따로 필요&lt;/strong&gt; 하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;공기스프링은 측면 강성이 약하다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;공기스프링&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;공기는 위아래로 눌리는 데는 잘 버티지만 옆으로 밀리면 주머니가 그대로 기운다&lt;/strong&gt; — &lt;strong&gt;그래서 옆방향을 잡아 줄 다른 장치가 따로 필요&lt;/strong&gt;하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;공기스프링은 측면 강성이 약하다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -7628,7 +7628,7 @@
       </c>
       <c r="AH51" s="32" t="inlineStr">
         <is>
-          <t>① 50 [lux] 는 기준에 못 미친다.&lt;br&gt;③ 90 [lux] 는 기준값이 아니다.&lt;br&gt;④ 100 [lux] 도 그렇다.</t>
+          <t>① 50 [lux]는 기준에 못 미친다.&lt;br&gt;③ 90 [lux]는 기준값이 아니다.&lt;br&gt;④ 100 [lux] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI51" s="32" t="inlineStr">
@@ -7881,17 +7881,17 @@
       </c>
       <c r="AG53" s="32" t="inlineStr">
         <is>
-          <t>$S = 1.6 t$ [m/s] 다. &lt;strong&gt;사람의 손이 뻗는 속도를 1.6 [m/s] 로 잡은&lt;/strong&gt; 값이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전거리의 계수&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일반 안전거리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$S = 1.6 t$ [m]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;t 는 총 제동 소요시간 [초]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;같은 뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$S = 1 {,} 600 t$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1.6 [m/s] = 1,600 [mm/s]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;양수기동식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D_{m} = 1 {,} 600 T_{m}$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;양수조작식·광전자식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1 {,} 600 ( T_{c} + T_{s} )$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$S = 1.6 t$ [m/s]다. &lt;strong&gt;사람의 손이 뻗는 속도를 1.6 [m/s]로 잡은&lt;/strong&gt; 값이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전거리의 계수&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;일반 안전거리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$S = 1.6 t$ [m]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;t는 총 제동 소요시간 [초]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;같은 뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$S = 1 {,} 600 t$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;1.6 [m/s] = 1,600 [mm/s]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;양수기동식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D_{m} = 1 {,} 600 T_{m}$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;양수조작식·광전자식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1 {,} 600 ( T_{c} + T_{s} )$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH53" s="32" t="inlineStr">
         <is>
-          <t>① 1.0t 는 기준 계수가 아니다.&lt;br&gt;③ 2.8t 도 아니다.&lt;br&gt;④ 3.2t 도 아니다.</t>
+          <t>① 1.0t는 기준 계수가 아니다.&lt;br&gt;③ 2.8t 도 아니다.&lt;br&gt;④ 3.2t 도 아니다.</t>
         </is>
       </c>
       <c r="AI53" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1.6 [m/s] 는 사람이 손을 뻗는 속도&lt;/strong&gt;다 — &lt;strong&gt;「그 시간 동안 손이 갈 수 있는 거리만큼 떼어 놓는다」&lt;/strong&gt;는 것이 모든 안전거리 식의 뜻이다. &lt;strong&gt;단위가 [m] 인지 [mm] 인지&lt;/strong&gt;만 갈라 보면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $S = 1.6 t$ [m].&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방호장치의 안전거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1.6 [m/s]는 사람이 손을 뻗는 속도&lt;/strong&gt;다 — &lt;strong&gt;「그 시간 동안 손이 갈 수 있는 거리만큼 떼어 놓는다」&lt;/strong&gt;는 것이 모든 안전거리 식의 뜻이다. &lt;strong&gt;단위가 [m] 인지 [mm] 인지&lt;/strong&gt;만 갈라 보면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $S = 1.6 t$ [m].&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8010,17 +8010,17 @@
       </c>
       <c r="AG54" s="32" t="inlineStr">
         <is>
-          <t>$T_{m} = ( \dfrac{1}{\text{클러치 개소수}} + \dfrac{1}{2} ) \times \dfrac{60 {,} 000}{\mathrm{SPM}} = ( 0.25 + 0.5 ) \times 600 = 450$ [ms] 다. $D = 1.6 \times 450 = 720$ [mm] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;양수조작식 방호장치의 설치거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① &lt;/u&gt;$T_{m}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$( \dfrac{1}{\text{클러치 개소수}} + \dfrac{1}{2} ) \times \dfrac{60 {,} 000}{\mathrm{SPM}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;[ms]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;(1/4 + 1/2) × 600 = 450 [ms]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 안전거리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1.6 T_{m}$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.6 × 450 = 720 [mm]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$T_{m} = ( \dfrac{1}{\text{클러치 개소수}} + \dfrac{1}{2} ) \times \dfrac{60 {,} 000}{\mathrm{SPM}} = ( 0.25 + 0.5 ) \times 600 = 450$ [ms]다. $D = 1.6 \times 450 = 720$ [mm]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;양수조작식 방호장치의 설치거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① &lt;/u&gt;$T_{m}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$( \dfrac{1}{\text{클러치 개소수}} + \dfrac{1}{2} ) \times \dfrac{60 {,} 000}{\mathrm{SPM}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;[ms]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;(1/4 + 1/2) × 600 = 450 [ms]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 안전거리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1.6 T_{m}$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.6 × 450 = 720 [mm]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH54" s="32" t="inlineStr">
         <is>
-          <t>① 160 [mm] 는 계산과 맞지 않는다.&lt;br&gt;② 240 [mm] 도 그렇다.&lt;br&gt;③ 300 [mm] 는 누름버튼 사이의 거리 기준이다.</t>
+          <t>① 160 [mm]는 계산과 맞지 않는다.&lt;br&gt;② 240 [mm] 도 그렇다.&lt;br&gt;③ 300 [mm]는 누름버튼 사이의 거리 기준이다.</t>
         </is>
       </c>
       <c r="AI54" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;양수조작식 방호장치의 설치거리&lt;/strong&gt;&lt;br&gt;$\dfrac{60 {,} 000}{\mathrm{SPM}}$ 은 &lt;strong&gt;1행정에 걸리는 시간 [ms]&lt;/strong&gt;이다 — &lt;strong&gt;SPM 100 이면 600 [ms]&lt;/strong&gt;. &lt;strong&gt;거기에 「클러치가 물릴 때까지의 몫 + 반 행정」&lt;/strong&gt;을 곱한 것이 $T_{m}$ 이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $T_{m} = ( 1 / \text{클러치} + 1 / 2 ) \times 60 {,} 000 / \mathrm{SPM}$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;양수조작식 방호장치의 설치거리&lt;/strong&gt;&lt;br&gt;$\dfrac{60 {,} 000}{\mathrm{SPM}}$은 &lt;strong&gt;1행정에 걸리는 시간 [ms]&lt;/strong&gt;이다 — &lt;strong&gt;SPM 100 이면 600 [ms]&lt;/strong&gt;. &lt;strong&gt;거기에 「클러치가 물릴 때까지의 몫 + 반 행정」&lt;/strong&gt;을 곱한 것이 $T_{m}$이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $T_{m} = ( 1 / \text{클러치} + 1 / 2 ) \times 60 {,} 000 / \mathrm{SPM}$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8144,12 +8144,12 @@
       </c>
       <c r="AH55" s="32" t="inlineStr">
         <is>
-          <t>① 1.0 [m] 는 사람이 넘기 쉽다.&lt;br&gt;② 1.5 [m] 도 기준에 못 미친다.&lt;br&gt;④ 2.5 [m] 는 기준보다 높다.</t>
+          <t>① 1.0 [m]는 사람이 넘기 쉽다.&lt;br&gt;② 1.5 [m] 도 기준에 못 미친다.&lt;br&gt;④ 2.5 [m]는 기준보다 높다.</t>
         </is>
       </c>
       <c r="AI55" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;산업용 로봇의 방호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1.8 [m] 는 어른이 넘어 들어가기 어려운 높이&lt;/strong&gt;다 — &lt;strong&gt;로봇의 팔은 예고 없이 빠르게 움직이므로 사람이 그 반경 안에 들어가지 못하게&lt;/strong&gt; 막는 것이 최선이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;로봇 방책은 1.8 [m] 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;산업용 로봇의 방호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1.8 [m]는 어른이 넘어 들어가기 어려운 높이&lt;/strong&gt;다 — &lt;strong&gt;로봇의 팔은 예고 없이 빠르게 움직이므로 사람이 그 반경 안에 들어가지 못하게&lt;/strong&gt; 막는 것이 최선이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;로봇 방책은 1.8 [m] 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="AH61" s="32" t="inlineStr">
         <is>
-          <t>① 0.2 ~ 0.4 [m] 는 기준이 아니다.&lt;br&gt;③ 0.8 ~ 1.1 [m] 는 복부조작식의 위치다.&lt;br&gt;④ 1.8 [m] 이내는 손조작식의 위치다.</t>
+          <t>① 0.2 ~ 0.4 [m]는 기준이 아니다.&lt;br&gt;③ 0.8 ~ 1.1 [m]는 복부조작식의 위치다.&lt;br&gt;④ 1.8 [m] 이내는 손조작식의 위치다.</t>
         </is>
       </c>
       <c r="AI61" s="32" t="inlineStr">
@@ -9558,17 +9558,17 @@
       </c>
       <c r="AG66" s="32" t="inlineStr">
         <is>
-          <t>$I = \dfrac{165}{\sqrt{1}} = 165$ [mA] 이므로 $W = ( 0.165 )^{2} \times 500 \times 1 \fallingdotseq 13.6$ [J] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;심실세동과 위험한계 에너지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;심실세동전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$I = \dfrac{165}{\sqrt{T}}$ [mA]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;달지엘의 식&lt;/u&gt; · T 는 통전시간 [초]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험한계 에너지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$W = I^{2} R T$ [J]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R = 500 [Ω]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;13.6 [J]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R = 1,000 [Ω]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;27.23 [J]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;자주 함께 나온다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$I = \dfrac{165}{\sqrt{1}} = 165$ [mA]이므로 $W = ( 0.165 )^{2} \times 500 \times 1 \fallingdotseq 13.6$ [J]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;심실세동과 위험한계 에너지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;심실세동전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$I = \dfrac{165}{\sqrt{T}}$ [mA]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;달지엘의 식&lt;/u&gt; · T는 통전시간 [초]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험한계 에너지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$W = I^{2} R T$ [J]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R = 500 [Ω]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;13.6 [J]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R = 1,000 [Ω]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;27.23 [J]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;자주 함께 나온다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH66" s="32" t="inlineStr">
         <is>
-          <t>① 13.2 [J] 는 계산과 맞지 않는다.&lt;br&gt;② 13.4 [J] 도 그렇다.&lt;br&gt;④ 14.6 [J] 도 그렇다.</t>
+          <t>① 13.2 [J]는 계산과 맞지 않는다.&lt;br&gt;② 13.4 [J] 도 그렇다.&lt;br&gt;④ 14.6 [J] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI66" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;위험한계 에너지&lt;/strong&gt;&lt;br&gt;$W = I^{2} R T$ 에 $I = 165 / \sqrt{T}$ 를 넣으면 $T$&lt;strong&gt; 가 약분되어 저항만으로 정해진다&lt;/strong&gt; — &lt;strong&gt;500 이면 13.6, 1,000 이면 27.23&lt;/strong&gt; 두 값만 외워 두면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;500 [Ω] 이면 13.6 [J]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;위험한계 에너지&lt;/strong&gt;&lt;br&gt;$W = I^{2} R T$에 $I = 165 / \sqrt{T}$를 넣으면 $T$&lt;strong&gt;가 약분되어 저항만으로 정해진다&lt;/strong&gt; — &lt;strong&gt;500 이면 13.6, 1,000 이면 27.23&lt;/strong&gt; 두 값만 외워 두면 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;500 [Ω] 이면 13.6 [J]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9691,12 +9691,12 @@
       </c>
       <c r="AG67" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;감전을 막으려면 정격감도전류가 30 [mA] 이하&lt;/strong&gt; 라야 한다. &lt;strong&gt;값이 클수록 사람이 다친 뒤에야 끊긴다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;누전차단기의 정격 선정&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;감전방지용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [mA] 이하, 0.03초 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사람을 지킨다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물기가 있는 장소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;15 [mA] 이하, 0.03초 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고감도 고속형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [mA], 0.1초 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항의 정답&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;왜 30 [mA] 인가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사람이 스스로 손을 뗄 수 있는 한계(가수전류) 언저리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;감전을 막으려면 정격감도전류가 30 [mA] 이하&lt;/strong&gt;라야 한다. &lt;strong&gt;값이 클수록 사람이 다친 뒤에야 끊긴다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;누전차단기의 정격 선정&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;감전방지용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [mA] 이하, 0.03초 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사람을 지킨다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물기가 있는 장소&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;15 [mA] 이하, 0.03초 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고감도 고속형&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [mA], 0.1초 이내&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항의 정답&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;왜 30 [mA] 인가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사람이 스스로 손을 뗄 수 있는 한계(가수전류) 언저리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH67" s="32" t="inlineStr">
         <is>
-          <t>② 60 [mA] 는 이미 심실세동에 이를 수 있는 크기다.&lt;br&gt;③ 90 [mA] 도 그렇다.&lt;br&gt;④ 120 [mA] 도 그렇다.</t>
+          <t>② 60 [mA]는 이미 심실세동에 이를 수 있는 크기다.&lt;br&gt;③ 90 [mA] 도 그렇다.&lt;br&gt;④ 120 [mA] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI67" s="32" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="AH69" s="32" t="inlineStr">
         <is>
-          <t>① 머리 위 60, 발 아래 30 은 두 값을 뒤바꾼 것이다.&lt;br&gt;② 머리 위 30, 발 아래 40 은 뒤쪽 값이 맞지 않는다.&lt;br&gt;④ 머리 위 40, 발 아래 30 도 그렇다.</t>
+          <t>① 머리 위 60, 발 아래 30은 두 값을 뒤바꾼 것이다.&lt;br&gt;② 머리 위 30, 발 아래 40은 뒤쪽 값이 맞지 않는다.&lt;br&gt;④ 머리 위 40, 발 아래 30 도 그렇다.</t>
         </is>
       </c>
       <c r="AI69" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;충전전로 근접작업&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;머리 위가 더 좁다&lt;/strong&gt; — &lt;strong&gt;사람이 몸을 세우면 머리가 먼저 닿기&lt;/strong&gt; 때문이다. &lt;strong&gt;「30 · 60 · 55」&lt;/strong&gt; 세 숫자를 방향과 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;머리 위 30, 발 아래 60&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 충전전로 작업의 접근한계거리는 &lt;u&gt;안전보건기준규칙 제321조&lt;/u&gt;에 전압별로 따로 정해져 있다(예: 22.9 [kV] 는 90 [cm]). 이 문항의 30·60·55 는 &lt;u&gt;절연용 방호구 설치 판단 기준&lt;/u&gt;이므로 둘을 갈라 둘 것.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;충전전로 근접작업&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;머리 위가 더 좁다&lt;/strong&gt; — &lt;strong&gt;사람이 몸을 세우면 머리가 먼저 닿기&lt;/strong&gt; 때문이다. &lt;strong&gt;「30 · 60 · 55」&lt;/strong&gt; 세 숫자를 방향과 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;머리 위 30, 발 아래 60&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 충전전로 작업의 접근한계거리는 &lt;u&gt;안전보건기준규칙 제321조&lt;/u&gt;에 전압별로 따로 정해져 있다(예: 22.9 [kV]는 90 [cm]). 이 문항의 30·60·55는 &lt;u&gt;절연용 방호구 설치 판단 기준&lt;/u&gt;이므로 둘을 갈라 둘 것.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10079,7 +10079,7 @@
       </c>
       <c r="AH70" s="32" t="inlineStr">
         <is>
-          <t>① 2.5 [V] 이하는 물에 젖은 제1종의 값이다.&lt;br&gt;③ 42 [V] 는 종별 기준에 없다.&lt;br&gt;④ 사람에 따라 다르다는 것은 기준이 될 수 없다.</t>
+          <t>① 2.5 [V] 이하는 물에 젖은 제1종의 값이다.&lt;br&gt;③ 42 [V]는 종별 기준에 없다.&lt;br&gt;④ 사람에 따라 다르다는 것은 기준이 될 수 없다.</t>
         </is>
       </c>
       <c r="AI70" s="32" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="AI71" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;분진폭발&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「이미 다 탄 것」은 다시 타지 않는다&lt;/strong&gt; — &lt;strong&gt;산화물(CaO)이나 무기 광물(시멘트 · 모래)이 그것&lt;/strong&gt;이다. &lt;strong&gt;금속분과 유기물 가루는 거의 다 위험&lt;/strong&gt; 하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;생석회는 분진폭발하지 않는다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;분진폭발&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「이미 다 탄 것」은 다시 타지 않는다&lt;/strong&gt; — &lt;strong&gt;산화물(CaO)이나 무기 광물(시멘트 · 모래)이 그것&lt;/strong&gt;이다. &lt;strong&gt;금속분과 유기물 가루는 거의 다 위험&lt;/strong&gt;하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;생석회는 분진폭발하지 않는다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="AI74" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;전기기계·기구 조작 시의 안전조치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;70 [cm] 는 사람이 몸을 돌려 일할 수 있는 폭&lt;/strong&gt;이다 — &lt;strong&gt;좁으면 뒤로 물러설 수 없어 감전 시 빠져나오지 못한다&lt;/strong&gt;. &lt;strong&gt;「150 · 70 · 600」&lt;/strong&gt; 세 숫자가 이 조문의 전부다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작업공간은 폭 70 [cm] 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;전기기계·기구 조작 시의 안전조치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;70 [cm]는 사람이 몸을 돌려 일할 수 있는 폭&lt;/strong&gt;이다 — &lt;strong&gt;좁으면 뒤로 물러설 수 없어 감전 시 빠져나오지 못한다&lt;/strong&gt;. &lt;strong&gt;「150 · 70 · 600」&lt;/strong&gt; 세 숫자가 이 조문의 전부다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작업공간은 폭 70 [cm] 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10848,12 +10848,12 @@
       </c>
       <c r="AG76" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;검전기&lt;/strong&gt;다. &lt;strong&gt;전기가 살아 있는지 확인&lt;/strong&gt; 하는 기구다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;비슷한 기기 가르기&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기기&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;검전기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;충전 유무를 확인한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; · 저압용 · 고압용&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위상검출기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상(phase)의 차례를 확인한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;디스콘 스위치(DS)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;단로기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;무부하 선로의 개폐&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;COS&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;컷아웃 스위치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;변압기 1차측 보호&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;검전기&lt;/strong&gt;다. &lt;strong&gt;전기가 살아 있는지 확인&lt;/strong&gt;하는 기구다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;비슷한 기기 가르기&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기기&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;검전기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;충전 유무를 확인한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt; · 저압용 · 고압용&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위상검출기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상(phase)의 차례를 확인한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;디스콘 스위치(DS)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;단로기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;무부하 선로의 개폐&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;COS&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;컷아웃 스위치&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;변압기 1차측 보호&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH76" s="32" t="inlineStr">
         <is>
-          <t>① 위상검출기는 상의 차례를 확인하는 기기다.&lt;br&gt;② 디스콘 스위치는 단로기다.&lt;br&gt;③ COS 는 변압기 1차측을 보호하는 컷아웃 스위치다.</t>
+          <t>① 위상검출기는 상의 차례를 확인하는 기기다.&lt;br&gt;② 디스콘 스위치는 단로기다.&lt;br&gt;③ COS는 변압기 1차측을 보호하는 컷아웃 스위치다.</t>
         </is>
       </c>
       <c r="AI76" s="32" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AI80" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;전기 기계·기구의 설치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;세 가지가 「용량과 강도 · 주위 환경 · 방호수단」&lt;/strong&gt; 뿐이다 — &lt;strong&gt;셋만 외워 두면 넷째로 무엇이 오든 걸러낼 수&lt;/strong&gt; 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;용량·강도 · 주위 환경 · 방호수단&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;전기 기계·기구의 설치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;세 가지가 「용량과 강도 · 주위 환경 · 방호수단」&lt;/strong&gt;뿐이다 — &lt;strong&gt;셋만 외워 두면 넷째로 무엇이 오든 걸러낼 수&lt;/strong&gt; 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;용량·강도 · 주위 환경 · 방호수단&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="AG86" s="32" t="inlineStr">
         <is>
-          <t>니트로셀룰로오스는 &lt;strong&gt;마르면 위험&lt;/strong&gt; 하다. &lt;strong&gt;물이나 알코올에 적셔 보관&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;니트로셀룰로오스(질화면)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;분류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;자기반응성물질(제5류) — 질산에스테르류&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;저장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;물이나 알코올에 적셔 둔다&lt;/u&gt; — 「건조 상태 유지」가 아니다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전용제&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;에탄올 · 이소프로필알코올 등&lt;/u&gt; — 자연발화를 막는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;금기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;충격 · 마찰 · 직사광선 · 고온&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;소화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다량의 물로 냉각소화&lt;/u&gt; — 제 안에 산소가 있어 질식소화가 듣지 않는다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>니트로셀룰로오스는 &lt;strong&gt;마르면 위험&lt;/strong&gt;하다. &lt;strong&gt;물이나 알코올에 적셔 보관&lt;/strong&gt;한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;니트로셀룰로오스(질화면)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;분류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;자기반응성물질(제5류) — 질산에스테르류&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;저장&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;물이나 알코올에 적셔 둔다&lt;/u&gt; — 「건조 상태 유지」가 아니다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전용제&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;에탄올 · 이소프로필알코올 등&lt;/u&gt; — 자연발화를 막는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;금기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;충격 · 마찰 · 직사광선 · 고온&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;소화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;다량의 물로 냉각소화&lt;/u&gt; — 제 안에 산소가 있어 질식소화가 듣지 않는다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH86" s="32" t="inlineStr">
@@ -12522,12 +12522,12 @@
       </c>
       <c r="AH89" s="32" t="inlineStr">
         <is>
-          <t>① 49 [kPa] 는 기준값이 아니다.&lt;br&gt;② 98 [kPa] 도 그렇다.&lt;br&gt;④ 196 [kPa] 도 그렇다.</t>
+          <t>① 49 [kPa]는 기준값이 아니다.&lt;br&gt;② 98 [kPa] 도 그렇다.&lt;br&gt;④ 196 [kPa] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI89" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;아세틸렌 용접장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;아세틸렌은 압력이 오르면 산소 없이도 스스로 분해 폭발&lt;/strong&gt; 한다 — &lt;strong&gt;127 [kPa] 라는 낮은 한계&lt;/strong&gt;가 그 때문이다. &lt;strong&gt;구리·은과 만나면 폭발성 화합물이 생긴다&lt;/strong&gt;는 것도 짝으로 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;아세틸렌은 127 [kPa] 이하&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;아세틸렌 용접장치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;아세틸렌은 압력이 오르면 산소 없이도 스스로 분해 폭발&lt;/strong&gt;한다 — &lt;strong&gt;127 [kPa]라는 낮은 한계&lt;/strong&gt;가 그 때문이다. &lt;strong&gt;구리·은과 만나면 폭발성 화합물이 생긴다&lt;/strong&gt;는 것도 짝으로 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;아세틸렌은 127 [kPa] 이하&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12650,12 +12650,12 @@
       </c>
       <c r="AG90" s="32" t="inlineStr">
         <is>
-          <t>$\Delta H = ( 2 \times (-94.052 ) + (-57.798 ) ) - 54.194 \fallingdotseq - 300.1$ [kcal/mol] 이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;반응열의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\Delta H = \sum \text{생성물의 생성열} - \sum \text{반응물의 생성열}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;생성물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 × (−94.052) + (−57.798) = −245.902&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반응물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;54.194&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;O&lt;/u&gt;$"_{2}$&lt;u&gt; 는 홑원소물질이라 0&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연소열&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−245.902 − 54.194 = −300.1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;발열이므로 음(−)&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$\Delta H = ( 2 \times (-94.052 ) + (-57.798 ) ) - 54.194 \fallingdotseq - 300.1$ [kcal/mol]이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;반응열의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\Delta H = \sum \text{생성물의 생성열} - \sum \text{반응물의 생성열}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;생성물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2 × (−94.052) + (−57.798) = −245.902&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반응물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;54.194&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;O&lt;/u&gt;$"_{2}$&lt;u&gt;는 홑원소물질이라 0&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연소열&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;−245.902 − 54.194 = −300.1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;발열이므로 음(−)&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH90" s="32" t="inlineStr">
         <is>
-          <t>② −200.1 은 계산과 맞지 않는다.&lt;br&gt;③ 200.1 은 부호가 반대다.&lt;br&gt;④ 300.1 도 부호가 반대다.</t>
+          <t>② −200.1은 계산과 맞지 않는다.&lt;br&gt;③ 200.1은 부호가 반대다.&lt;br&gt;④ 300.1 도 부호가 반대다.</t>
         </is>
       </c>
       <c r="AI90" s="32" t="inlineStr">
@@ -12908,7 +12908,7 @@
       </c>
       <c r="AG92" s="32" t="inlineStr">
         <is>
-          <t>위험물은 &lt;strong&gt;구조와 결합이 불안정&lt;/strong&gt; 하다. &lt;strong&gt;그래서 작은 자극에도 반응한다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;위험물의 일반적 특성&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;특성&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;화학적 구조와 결합이 불안정하다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「안정되어 있다」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반응할 때 내는 열량이 크다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물이나 산소와 쉽게 반응한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소 같은 가연성 가스를 낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반응속도가 빠르고 폭발성을 띤다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>위험물은 &lt;strong&gt;구조와 결합이 불안정&lt;/strong&gt;하다. &lt;strong&gt;그래서 작은 자극에도 반응한다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;위험물의 일반적 특성&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;특성&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;화학적 구조와 결합이 불안정하다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「안정되어 있다」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반응할 때 내는 열량이 크다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;물이나 산소와 쉽게 반응한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수소 같은 가연성 가스를 낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;반응속도가 빠르고 폭발성을 띤다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH92" s="32" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="AG96" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전밸브&lt;/strong&gt;다. &lt;strong&gt;설정압력을 넘으면 열려 압력을 뺀다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전밸브를 설치해야 하는 설비&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;설비&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;압력용기(안지름 150 [mm] 이하는 제외)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안지름 150 [mm] 를 넘으면&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정변위 압축기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정변위 펌프(토출축에 차단밸브가 있는 것)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;배관(2개 이상의 밸브로 차단되어 열팽창의 우려가 있는 것)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;그 밖에 최고사용압력을 넘을 우려가 있는 설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;안전밸브&lt;/strong&gt;다. &lt;strong&gt;설정압력을 넘으면 열려 압력을 뺀다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전밸브를 설치해야 하는 설비&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;설비&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;압력용기(안지름 150 [mm] 이하는 제외)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안지름 150 [mm]를 넘으면&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정변위 압축기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정변위 펌프(토출축에 차단밸브가 있는 것)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;배관(2개 이상의 밸브로 차단되어 열팽창의 우려가 있는 것)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;그 밖에 최고사용압력을 넘을 우려가 있는 설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH96" s="32" t="inlineStr">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="AG99" s="32" t="inlineStr">
         <is>
-          <t>위험물 건조설비에는 &lt;strong&gt;직화를 쓰지 않는다&lt;/strong&gt;. &lt;strong&gt;부득이 쓸 때는 불꽃이 닿지 않도록 막을 설치&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;건조설비의 구조&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;바깥 면은 불연성 재료로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내부는 청소하기 쉬운 구조로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내부 온도가 국부적으로 오르지 않는 구조로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험물 건조설비의 열원으로 직화를 쓰지 말 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;부득이하면 불꽃 등에 의한 화재를 막을 조치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;건조 중 나오는 가스·증기·분진을 밖으로 내보낼 설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;측정장치와 안전장치(폭발구·안전밸브)를 갖출 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>위험물 건조설비에는 &lt;strong&gt;직화를 쓰지 않는다&lt;/strong&gt;. &lt;strong&gt;부득이 쓸 때는 불꽃이 닿지 않도록 막을 설치&lt;/strong&gt;한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;건조설비의 구조&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;바깥 면은 불연성 재료로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내부는 청소하기 쉬운 구조로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내부 온도가 국부적으로 오르지 않는 구조로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험물 건조설비의 열원으로 직화를 쓰지 말 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;부득이하면 불꽃 등에 의한 화재를 막을 조치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;건조 중 나오는 가스·증기·분진을 밖으로 내보낼 설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;측정장치와 안전장치(폭발구·안전밸브)를 갖출 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH99" s="32" t="inlineStr">
@@ -14061,7 +14061,7 @@
       </c>
       <c r="AG101" s="32" t="inlineStr">
         <is>
-          <t>액체연료는 &lt;strong&gt;시간당 10 [kg] 이상&lt;/strong&gt; 이라야 대상이다. &lt;strong&gt;「5 [kg/h]」가 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;독립된 단층 건물로 해야 하는 건조설비&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험물 또는 위험물이 발생하는 물질을 가열·건조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;내용적 1 [m³] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험물이 아닌 물질 — 고체연료&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최대사용량 시간당 10 [kg] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험물이 아닌 물질 — 액체연료&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최대사용량 시간당 10 [kg] 이상&lt;/u&gt; — 「5 [kg/h]」가 아니다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험물이 아닌 물질 — 기체연료&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최대사용량 시간당 1 [m³] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험물이 아닌 물질 — 전열&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정격용량 10 [kW] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>액체연료는 &lt;strong&gt;시간당 10 [kg] 이상&lt;/strong&gt;이라야 대상이다. &lt;strong&gt;「5 [kg/h]」가 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;독립된 단층 건물로 해야 하는 건조설비&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구분&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험물 또는 위험물이 발생하는 물질을 가열·건조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;내용적 1 [m³] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험물이 아닌 물질 — 고체연료&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최대사용량 시간당 10 [kg] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험물이 아닌 물질 — 액체연료&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최대사용량 시간당 10 [kg] 이상&lt;/u&gt; — 「5 [kg/h]」가 아니다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험물이 아닌 물질 — 기체연료&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최대사용량 시간당 1 [m³] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험물이 아닌 물질 — 전열&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정격용량 10 [kW] 이상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH101" s="32" t="inlineStr">
@@ -14071,7 +14071,7 @@
       </c>
       <c r="AI101" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;위험물 건조설비의 건축물 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;숫자가 「1 · 10 · 10 · 1 · 10」&lt;/strong&gt;이다 — &lt;strong&gt;고체와 액체 연료는 10 [kg/h], 기체는 1 [m³/h], 전열은 10 [kW], 위험물은 내용적 1 [m³]&lt;/strong&gt;. &lt;strong&gt;액체만 5 로 낮춰 놓은&lt;/strong&gt; 것이 이 문항이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;액체연료는 10 [kg/h] 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;위험물 건조설비의 건축물 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;숫자가 「1 · 10 · 10 · 1 · 10」&lt;/strong&gt;이다 — &lt;strong&gt;고체와 액체 연료는 10 [kg/h], 기체는 1 [m³/h], 전열은 10 [kW], 위험물은 내용적 1 [m³]&lt;/strong&gt;. &lt;strong&gt;액체만 5로 낮춰 놓은&lt;/strong&gt; 것이 이 문항이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;액체연료는 10 [kg/h] 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14453,12 +14453,12 @@
       </c>
       <c r="AH104" s="32" t="inlineStr">
         <is>
-          <t>① 200 [kg] 은 10 [cm] 매듭방망의 신품 기준이다.&lt;br&gt;② 100 [kg] 은 기준값이 아니다.&lt;br&gt;④ 30 [kg] 도 기준값이 아니다.</t>
+          <t>① 200 [kg]은 10 [cm] 매듭방망의 신품 기준이다.&lt;br&gt;② 100 [kg]은 기준값이 아니다.&lt;br&gt;④ 30 [kg] 도 기준값이 아니다.</t>
         </is>
       </c>
       <c r="AI104" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방망사의 인장강도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;네 값이 「240 / 150 · 200 / 135」이고 5 [cm] 매듭만 「110 / 60」&lt;/strong&gt;이다. &lt;strong&gt;5 [cm] 는 매듭방망에만 있다&lt;/strong&gt;는 점도 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;5 [cm] 매듭 폐기는 60 [kg]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방망사의 인장강도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;네 값이 「240 / 150 · 200 / 135」이고 5 [cm] 매듭만 「110 / 60」&lt;/strong&gt;이다. &lt;strong&gt;5 [cm]는 매듭방망에만 있다&lt;/strong&gt;는 점도 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;5 [cm] 매듭 폐기는 60 [kg]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14706,17 +14706,17 @@
       </c>
       <c r="AG106" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;10 [m] 를 넘지 않게&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;추락방호망의 설치기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업면에서 망까지 수직거리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [m] 를 넘지 않을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내민 길이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;벽면에서 3 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;처짐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;짧은 변 길이의 12% 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;겹침&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이어 쓸 때 60 [cm] 이상 겹치거나 묶을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;10 [m]를 넘지 않게&lt;/strong&gt; 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;추락방호망의 설치기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업면에서 망까지 수직거리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [m]를 넘지 않을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내민 길이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;벽면에서 3 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;처짐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;짧은 변 길이의 12% 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;겹침&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이어 쓸 때 60 [cm] 이상 겹치거나 묶을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH106" s="32" t="inlineStr">
         <is>
-          <t>① 5 [m] 는 기준값이 아니다.&lt;br&gt;② 7 [m] 도 그렇다.&lt;br&gt;③ 8 [m] 도 그렇다.</t>
+          <t>① 5 [m]는 기준값이 아니다.&lt;br&gt;② 7 [m] 도 그렇다.&lt;br&gt;③ 8 [m] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI106" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;추락방호망&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;10 [m] 는 「이 정도 높이에서 떨어져도 방망이 받아 낼 수 있다」&lt;/strong&gt;는 한계다 — &lt;strong&gt;더 높으면 방망 자체가 찢어지거나 바닥에 닿는다&lt;/strong&gt;. &lt;strong&gt;「10 · 3 · 12% · 60」&lt;/strong&gt; 네 숫자로 붙든다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;수직거리 10 [m] 이하&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;추락방호망&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;10 [m]는 「이 정도 높이에서 떨어져도 방망이 받아 낼 수 있다」&lt;/strong&gt;는 한계다 — &lt;strong&gt;더 높으면 방망 자체가 찢어지거나 바닥에 닿는다&lt;/strong&gt;. &lt;strong&gt;「10 · 3 · 12% · 60」&lt;/strong&gt; 네 숫자로 붙든다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;수직거리 10 [m] 이하&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14845,7 +14845,7 @@
       </c>
       <c r="AI107" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;차량계 건설기계의 작업계획서&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;세 항목이 「무엇으로 · 어디로 · 어떻게」&lt;/strong&gt; 뿐이다 — &lt;strong&gt;넷째로 무엇이 오든 그것이 답&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;종류·성능 · 운행경로 · 작업방법&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;차량계 건설기계의 작업계획서&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;세 항목이 「무엇으로 · 어디로 · 어떻게」&lt;/strong&gt;뿐이다 — &lt;strong&gt;넷째로 무엇이 오든 그것이 답&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;종류·성능 · 운행경로 · 작업방법&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14964,7 +14964,7 @@
       </c>
       <c r="AG108" s="32" t="inlineStr">
         <is>
-          <t>비계는 &lt;strong&gt;높이 31 [m] 이상&lt;/strong&gt; 이라야 대상이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;설계변경을 요청할 수 있는 가설구조물&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가설구조물&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 31 [m] 이상인 비계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「20 [m]」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업발판 일체형 거푸집 또는 높이 6 [m] 이상인 거푸집 동바리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;터널의 지보공 또는 높이 2 [m] 이상인 흙막이 지보공&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;동력을 이용하여 움직이는 가설구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 10 [m] 이상에서 외부작업을 하기 위해 작업발판과 안전난간을 일체화한 가설구조물(현장조립 작업대)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;그 밖에 발주자·인허가기관의 장이 필요하다고 인정하는 가설구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>비계는 &lt;strong&gt;높이 31 [m] 이상&lt;/strong&gt;이라야 대상이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;설계변경을 요청할 수 있는 가설구조물&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가설구조물&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 31 [m] 이상인 비계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「20 [m]」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업발판 일체형 거푸집 또는 높이 6 [m] 이상인 거푸집 동바리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;터널의 지보공 또는 높이 2 [m] 이상인 흙막이 지보공&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;동력을 이용하여 움직이는 가설구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;높이 10 [m] 이상에서 외부작업을 하기 위해 작업발판과 안전난간을 일체화한 가설구조물(현장조립 작업대)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;그 밖에 발주자·인허가기관의 장이 필요하다고 인정하는 가설구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH108" s="32" t="inlineStr">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="AI108" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;가설구조물의 설계변경 요청&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「31 · 6 · 2 · 10」&lt;/strong&gt; 네 숫자다. &lt;strong&gt;31 [m] 는 유해위험방지계획서의 「지상높이 31 [m] 이상」과 같은 값&lt;/strong&gt;이라 짝지어 외워 두면 편하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;비계는 31 [m] 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;가설구조물의 설계변경 요청&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「31 · 6 · 2 · 10」&lt;/strong&gt; 네 숫자다. &lt;strong&gt;31 [m]는 유해위험방지계획서의 「지상높이 31 [m] 이상」과 같은 값&lt;/strong&gt;이라 짝지어 외워 두면 편하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;비계는 31 [m] 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AG109" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;지상높이 31 [m] 이상&lt;/strong&gt; 이라야 대상이다. &lt;strong&gt;「25 [m]」가 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;건설업 유해위험방지계획서 제출 대상&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지상높이 31 [m] 이상인 건축물 또는 인공구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「25 [m]」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연면적 30,000 [m²] 이상인 건축물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연면적 5,000 [m²] 이상인 문화·집회시설, 판매·운수시설, 종교시설, 종합병원, 관광숙박시설, 지하도상가, 냉동·냉장 창고시설&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연면적 5,000 [m²] 이상인 냉동·냉장 창고시설의 설비공사·단열공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최대 지간길이 50 [m] 이상인 다리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;터널의 건설등 공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;다목적댐·발전용댐, 저수용량 2천만 톤 이상의 용수전용댐·지방상수도 전용댐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;깊이 10 [m] 이상인 굴착공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;지상높이 31 [m] 이상&lt;/strong&gt;이라야 대상이다. &lt;strong&gt;「25 [m]」가 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;건설업 유해위험방지계획서 제출 대상&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지상높이 31 [m] 이상인 건축물 또는 인공구조물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「25 [m]」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연면적 30,000 [m²] 이상인 건축물&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연면적 5,000 [m²] 이상인 문화·집회시설, 판매·운수시설, 종교시설, 종합병원, 관광숙박시설, 지하도상가, 냉동·냉장 창고시설&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;연면적 5,000 [m²] 이상인 냉동·냉장 창고시설의 설비공사·단열공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최대 지간길이 50 [m] 이상인 다리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;터널의 건설등 공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;다목적댐·발전용댐, 저수용량 2천만 톤 이상의 용수전용댐·지방상수도 전용댐&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;깊이 10 [m] 이상인 굴착공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH109" s="32" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="AI109" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;유해위험방지계획서 제출 대상&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「31 · 30,000 · 5,000 · 50 · 2천만 · 10」&lt;/strong&gt; 여섯 숫자다. &lt;strong&gt;31 [m] 는 열 층 남짓한 건물의 높이&lt;/strong&gt;로 새겨 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;지상높이 31 [m] 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;유해위험방지계획서 제출 대상&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「31 · 30,000 · 5,000 · 50 · 2천만 · 10」&lt;/strong&gt; 여섯 숫자다. &lt;strong&gt;31 [m]는 열 층 남짓한 건물의 높이&lt;/strong&gt;로 새겨 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;지상높이 31 [m] 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15222,7 +15222,7 @@
       </c>
       <c r="AG110" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;지상높이 30 [m] 는 31 [m] 에 못 미친다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;보기별 판정&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;판정&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지상높이 30 [m]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;31 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대상이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최대 지간길이 50 [m] 교량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;50 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;대상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;터널 건설공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모두&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;대상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;깊이 11 [m] 굴착공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;대상&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;지상높이 30 [m]는 31 [m]에 못 미친다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;보기별 판정&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;판정&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지상높이 30 [m]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;31 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대상이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최대 지간길이 50 [m] 교량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;50 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;대상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;터널 건설공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모두&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;대상&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;깊이 11 [m] 굴착공사&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;대상&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH110" s="32" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="AI110" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;유해위험방지계획서 제출 대상&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「이상」이므로 딱 50 [m] 인 교량은 대상&lt;/strong&gt;이고 &lt;strong&gt;30 [m] 인 건물은 31 에 한 뼘 못 미쳐 대상이 아니다&lt;/strong&gt;. &lt;strong&gt;경계값을 한 칸씩 어긋나게 놓는 것&lt;/strong&gt;이 이 유형의 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;30 [m] 는 대상이 아니다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;유해위험방지계획서 제출 대상&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「이상」이므로 딱 50 [m] 인 교량은 대상&lt;/strong&gt;이고 &lt;strong&gt;30 [m] 인 건물은 31에 한 뼘 못 미쳐 대상이 아니다&lt;/strong&gt;. &lt;strong&gt;경계값을 한 칸씩 어긋나게 놓는 것&lt;/strong&gt;이 이 유형의 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;30 [m]는 대상이 아니다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15480,7 +15480,7 @@
       </c>
       <c r="AG112" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;최고속도가 시속 10 [km] 이하&lt;/strong&gt;인 기계는 제한속도를 따로 정하지 않아도 된다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;차량계 건설기계의 속도 관련 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제한속도를 정해야 하는 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최고속도가 시속 10 [km] 를 넘는 기계&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정하지 않아도 되는 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최고속도가 시속 10 [km] 이하인 기계&lt;/u&gt; — 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;누가 정하나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사업주가 작업장소의 지형과 지반 상태에 맞게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;운전자는&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정해진 제한속도를 지켜야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;최고속도가 시속 10 [km] 이하&lt;/strong&gt;인 기계는 제한속도를 따로 정하지 않아도 된다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;차량계 건설기계의 속도 관련 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;제한속도를 정해야 하는 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최고속도가 시속 10 [km]를 넘는 기계&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;정하지 않아도 되는 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;최고속도가 시속 10 [km] 이하인 기계&lt;/u&gt; — 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;누가 정하나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사업주가 작업장소의 지형과 지반 상태에 맞게&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;운전자는&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정해진 제한속도를 지켜야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH112" s="32" t="inlineStr">
@@ -15490,7 +15490,7 @@
       </c>
       <c r="AI112" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;차량계 건설기계의 제한속도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;시속 10 [km] 는 사람이 뛰는 속도 남짓&lt;/strong&gt;이다 — &lt;strong&gt;그보다 느리면 부딪쳐도 크게 다치지 않으므로 따로 제한을 걸지 않는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;시속 10 [km] 이하면 면제&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;차량계 건설기계의 제한속도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;시속 10 [km]는 사람이 뛰는 속도 남짓&lt;/strong&gt;이다 — &lt;strong&gt;그보다 느리면 부딪쳐도 크게 다치지 않으므로 따로 제한을 걸지 않는다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;시속 10 [km] 이하면 면제&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15738,17 +15738,17 @@
       </c>
       <c r="AG114" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;250 [kg]&lt;/strong&gt;을 넘지 않게 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;이동식 비계의 준수사항&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업발판의 최대 적재하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;250 [kg] 을 넘지 않을 것&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최대 높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;밑변 최소폭의 4배 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;바퀴&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;브레이크·쐐기 등으로 고정하고 아웃트리거를 설치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;승탑&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사람이 탄 채로 이동하지 말 것&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전난간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업발판 위에 설치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;250 [kg]&lt;/strong&gt;을 넘지 않게 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;이동식 비계의 준수사항&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;작업발판의 최대 적재하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;250 [kg]을 넘지 않을 것&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최대 높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;밑변 최소폭의 4배 이하&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;바퀴&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;브레이크·쐐기 등으로 고정하고 아웃트리거를 설치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;승탑&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사람이 탄 채로 이동하지 말 것&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전난간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업발판 위에 설치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH114" s="32" t="inlineStr">
         <is>
-          <t>① 350 [kg] 은 기준을 넘는다.&lt;br&gt;② 300 [kg] 도 그렇다.&lt;br&gt;④ 200 [kg] 은 기준보다 낮게 잡은 값이다.</t>
+          <t>① 350 [kg]은 기준을 넘는다.&lt;br&gt;② 300 [kg] 도 그렇다.&lt;br&gt;④ 200 [kg]은 기준보다 낮게 잡은 값이다.</t>
         </is>
       </c>
       <c r="AI114" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;이동식 비계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;바퀴가 달려 있어 흔들리기 쉬우므로 짐을 적게&lt;/strong&gt; 싣는다 — &lt;strong&gt;250 [kg] 과 「밑변 최소폭의 4배」&lt;/strong&gt; 두 숫자가 이동식 비계의 핵심이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작업발판 최대 적재하중 250 [kg]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;이동식 비계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;바퀴가 달려 있어 흔들리기 쉬우므로 짐을 적게&lt;/strong&gt; 싣는다 — &lt;strong&gt;250 [kg]과 「밑변 최소폭의 4배」&lt;/strong&gt; 두 숫자가 이동식 비계의 핵심이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작업발판 최대 적재하중 250 [kg]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15877,7 +15877,7 @@
       </c>
       <c r="AI115" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;선박승강설비&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「300 · 55 · 82」&lt;/strong&gt; 세 숫자다. &lt;strong&gt;55 [cm] 는 사람 하나가 지나는 너비, 82 [cm] 는 허리께 높이&lt;/strong&gt;로 새기면 잡기 쉽다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;300톤급 이상, 너비 55, 방책 82&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;선박승강설비&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「300 · 55 · 82」&lt;/strong&gt; 세 숫자다. &lt;strong&gt;55 [cm]는 사람 하나가 지나는 너비, 82 [cm]는 허리께 높이&lt;/strong&gt;로 새기면 잡기 쉽다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;300톤급 이상, 너비 55, 방책 82&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16130,7 +16130,7 @@
       </c>
       <c r="AH117" s="32" t="inlineStr">
         <is>
-          <t>① 문화재 0.2 [cm/s] 는 맞다.&lt;br&gt;② 주택·아파트 0.5 [cm/s] 도 맞다.&lt;br&gt;③ 상가 1.0 [cm/s] 도 맞다.</t>
+          <t>① 문화재 0.2 [cm/s]는 맞다.&lt;br&gt;② 주택·아파트 0.5 [cm/s] 도 맞다.&lt;br&gt;③ 상가 1.0 [cm/s] 도 맞다.</t>
         </is>
       </c>
       <c r="AI117" s="32" t="inlineStr">
@@ -16521,7 +16521,7 @@
       </c>
       <c r="AH120" s="32" t="inlineStr">
         <is>
-          <t>① 초당 20 [m] 는 기준값이 아니다.&lt;br&gt;② 초당 25 [m] 도 그렇다.&lt;br&gt;④ 초당 35 [m] 초과는 리프트·승강기의 붕괴 방지 기준이다.</t>
+          <t>① 초당 20 [m]는 기준값이 아니다.&lt;br&gt;② 초당 25 [m] 도 그렇다.&lt;br&gt;④ 초당 35 [m] 초과는 리프트·승강기의 붕괴 방지 기준이다.</t>
         </is>
       </c>
       <c r="AI120" s="32" t="inlineStr">
@@ -16650,7 +16650,7 @@
       </c>
       <c r="AH121" s="32" t="inlineStr">
         <is>
-          <t>② 200 [kg] 은 10 [cm] 매듭방망의 신품 기준이다.&lt;br&gt;③ 110 [kg] 은 5 [cm] 매듭방망의 신품 기준이다.&lt;br&gt;④ 80 [kg] 은 기준값이 아니다.</t>
+          <t>② 200 [kg]은 10 [cm] 매듭방망의 신품 기준이다.&lt;br&gt;③ 110 [kg]은 5 [cm] 매듭방망의 신품 기준이다.&lt;br&gt;④ 80 [kg]은 기준값이 아니다.</t>
         </is>
       </c>
       <c r="AI121" s="32" t="inlineStr">
@@ -16779,12 +16779,12 @@
       </c>
       <c r="AH122" s="32" t="inlineStr">
         <is>
-          <t>① 150 [kg] 은 10 [cm] 매듭없는 방망의 폐기기준이다.&lt;br&gt;③ 220 [kg] 은 기준값이 아니다.&lt;br&gt;④ 240 [kg] 은 10 [cm] 매듭없는 방망의 신품 기준이다.</t>
+          <t>① 150 [kg]은 10 [cm] 매듭없는 방망의 폐기기준이다.&lt;br&gt;③ 220 [kg]은 기준값이 아니다.&lt;br&gt;④ 240 [kg]은 10 [cm] 매듭없는 방망의 신품 기준이다.</t>
         </is>
       </c>
       <c r="AI122" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방망사의 인장강도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「매듭인가 아닌가」와 「신품인가 폐기인가」&lt;/strong&gt; 두 갈래를 모두 맞춰야 한다 — &lt;strong&gt;네 값 240 · 150 · 200 · 135 가 보기에 함께 놓여&lt;/strong&gt; 있어 한 갈래만 놓쳐도 틀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;10 [cm] 매듭 신품은 200 [kg]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방망사의 인장강도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「매듭인가 아닌가」와 「신품인가 폐기인가」&lt;/strong&gt; 두 갈래를 모두 맞춰야 한다 — &lt;strong&gt;네 값 240 · 150 · 200 · 135가 보기에 함께 놓여&lt;/strong&gt; 있어 한 갈래만 놓쳐도 틀린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;10 [cm] 매듭 신품은 200 [kg]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
